--- a/sample_outputs/golden_receipt_result.xlsx
+++ b/sample_outputs/golden_receipt_result.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>prepared_fixture_rule_extraction</t>
+          <t>course_example_rule_extraction</t>
         </is>
       </c>
     </row>
